--- a/req3-device/excel/HW01_TestSummaryReport.xlsx
+++ b/req3-device/excel/HW01_TestSummaryReport.xlsx
@@ -1,169 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="72" windowWidth="15252" windowHeight="7932" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="120" yWindow="72" windowWidth="15252" windowHeight="7932" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test summary report" sheetId="1" r:id="rId1"/>
-    <sheet name="Bug report" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Test summary report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bug report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Function ID</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Untested</t>
-  </si>
-  <si>
-    <t>Number of test cases</t>
-  </si>
-  <si>
-    <t>Function name</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Login as admin</t>
-  </si>
-  <si>
-    <t>Login as end user</t>
-  </si>
-  <si>
-    <t>TDHoang</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Problem summary</t>
-  </si>
-  <si>
-    <t>How to reproduce it</t>
-  </si>
-  <si>
-    <t>Reported by</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Assigned to</t>
-  </si>
-  <si>
-    <t>Login with blank User name not display error</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Enter User Name : " "
-2.Enter Password : "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>abcd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"
-3. Click "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" button</t>
-    </r>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF0070C0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -190,21 +70,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -217,22 +97,19 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Calibri"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color theme="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+      <border>
         <left/>
         <right/>
         <top style="thin">
@@ -244,25 +121,22 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Calibri"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color theme="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left/>
         <right/>
         <top style="thin">
@@ -275,21 +149,18 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Calibri"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color theme="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left/>
         <right/>
         <top style="thin">
@@ -302,11 +173,79 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G5" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="Function ID"/>
@@ -321,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I3" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table3" displayName="Table3" ref="A1:I3" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Function name" dataDxfId="3"/>
@@ -621,225 +560,329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" customWidth="1"/>
-    <col min="4" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col width="13.109375" customWidth="1" min="2" max="2"/>
+    <col width="29.6640625" customWidth="1" min="3" max="3"/>
+    <col width="10.6640625" customWidth="1" min="4" max="5"/>
+    <col width="11.33203125" customWidth="1" min="6" max="6"/>
+    <col width="21.6640625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="6" t="s">
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Nguyễn Phú Dinh (23120031)</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>[TỰ ĐIỀN] ngày</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Function ID</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Function name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Untested</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Number of test cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Điều khiển bằng nút bấm (bật/tắt, tốc độ)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <f>SUM(D4:F4)</f>
+        <v/>
+      </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8">
-        <v>41370</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành và hiệu năng cơ bản</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <f>SUM(D5:F5)</f>
+        <v/>
+      </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6">
+      <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>An toàn và độ chắc chắn cơ khí</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
+      <c r="G6">
+        <f>SUM(D6:F6)</f>
+        <v/>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="2"/>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D7">
+        <f>SUM(D4:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E4:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F4:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUM(G4:G6)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col width="5.33203125" customWidth="1" min="1" max="1"/>
+    <col width="21.5546875" customWidth="1" min="2" max="2"/>
+    <col width="25.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="26.6640625" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13.44140625" customWidth="1" min="7" max="7"/>
+    <col width="15.109375" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Function name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Problem summary</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>How to reproduce it</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Reported by</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Assigned to</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.2">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5">
-        <v>41370</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Điều khiển bằng nút bấm (bật/tắt, tốc độ)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>[TỰ ĐIỀN] Tóm tắt lỗi (nếu tìm thấy bug)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>[TỰ ĐIỀN] 1. ...
+2. ...</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23120031</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>[TỰ ĐIỀN] ngày</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="43.2">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5">
-        <v>41370</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-    </row>
+    <row r="3" ht="43.2" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/req3-device/excel/HW01_TestSummaryReport.xlsx
+++ b/req3-device/excel/HW01_TestSummaryReport.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.109375" customWidth="1" min="2" max="2"/>
@@ -598,10 +598,8 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>[TỰ ĐIỀN] ngày</t>
-        </is>
+      <c r="B2" s="8" t="n">
+        <v>46295</v>
       </c>
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6" t="n"/>
@@ -661,13 +659,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <f>SUM(D4:F4)</f>
@@ -689,13 +687,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <f>SUM(D5:F5)</f>
@@ -723,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <f>SUM(D6:F6)</f>
@@ -731,26 +729,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>Điều khiển đảo gió</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>SUM(D7:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D7">
-        <f>SUM(D4:D6)</f>
+      <c r="D8">
+        <f>SUM(D4:D7)</f>
         <v/>
       </c>
-      <c r="E7">
-        <f>SUM(E4:E6)</f>
+      <c r="E8">
+        <f>SUM(E4:E7)</f>
         <v/>
       </c>
-      <c r="F7">
-        <f>SUM(F4:F6)</f>
+      <c r="F8">
+        <f>SUM(F4:F7)</f>
         <v/>
       </c>
-      <c r="G7">
-        <f>SUM(G4:G6)</f>
+      <c r="G8">
+        <f>SUM(G4:G7)</f>
         <v/>
       </c>
     </row>
@@ -828,7 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>01</t>
@@ -841,13 +867,15 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>[TỰ ĐIỀN] Tóm tắt lỗi (nếu tìm thấy bug)</t>
+          <t>Hai nút tốc độ 1 và 2 cùng lún xuống khi nhấn đồng thời (không có cơ cấu khóa liên động)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>[TỰ ĐIỀN] 1. ...
-2. ...</t>
+          <t>1. Rút phích cắm, xác nhận quạt không có điện
+2. Dùng hai ngón tay nhấn nhẹ đồng thời nút 1 và nút 2
+3. Thả tay và quan sát trạng thái hai nút
+(Test case 01 - 005; video: https://youtube.com/shorts/NjJz7VyT0h4)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -855,10 +883,8 @@
           <t>23120031</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>[TỰ ĐIỀN] ngày</t>
-        </is>
+      <c r="F2" s="5" t="n">
+        <v>46295</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/req3-device/excel/HW01_TestSummaryReport.xlsx
+++ b/req3-device/excel/HW01_TestSummaryReport.xlsx
@@ -867,15 +867,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Hai nút tốc độ 1 và 2 cùng lún xuống khi nhấn đồng thời (không có cơ cấu khóa liên động)</t>
+          <t>[SV TỰ VIẾT] Tóm tắt lỗi (test case 01 - 005)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Rút phích cắm, xác nhận quạt không có điện
-2. Dùng hai ngón tay nhấn nhẹ đồng thời nút 1 và nút 2
-3. Thả tay và quan sát trạng thái hai nút
-(Test case 01 - 005; video: https://youtube.com/shorts/NjJz7VyT0h4)</t>
+          <t>[SV TỰ VIẾT] Các bước tái hiện</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/req3-device/excel/HW01_TestSummaryReport.xlsx
+++ b/req3-device/excel/HW01_TestSummaryReport.xlsx
@@ -867,12 +867,15 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>[SV TỰ VIẾT] Tóm tắt lỗi (test case 01 - 005)</t>
+          <t>Hai nút cùng lún xuống khi ấn</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>[SV TỰ VIẾT] Các bước tái hiện</t>
+          <t>1. Rút phích cắm và xác nhận quạt không có điện
+2. Dùng hai ngón tay nhấn nhẹ đồng thời nút 1 và nút 2
+3. Thả tay và quan sát trạng thái hai nút
+4. Nhấn nút Off để đưa quạt về trạng thái ban đầu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
